--- a/research/traditional_assets/database/data/vietnam/vietnam_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_software_system_application.xlsx
@@ -588,61 +588,64 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00874</v>
+        <v>0.0596</v>
       </c>
       <c r="E2">
-        <v>-0.00244</v>
+        <v>-0.00266</v>
       </c>
       <c r="G2">
-        <v>0.1387423935091278</v>
+        <v>0.1033722438391699</v>
       </c>
       <c r="H2">
-        <v>0.1387423935091278</v>
+        <v>0.1033722438391699</v>
       </c>
       <c r="I2">
-        <v>0.1269776876267749</v>
+        <v>0.1024643320363165</v>
       </c>
       <c r="J2">
-        <v>0.1071841069084835</v>
+        <v>0.08139806425756041</v>
       </c>
       <c r="K2">
-        <v>0.574</v>
+        <v>0.653</v>
       </c>
       <c r="L2">
-        <v>0.1164300202839757</v>
+        <v>0.08469520103761349</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.08427835051546392</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.5007656967840735</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.08427835051546392</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.5007656967840735</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>1.07</v>
+        <v>0.502</v>
       </c>
       <c r="V2">
-        <v>0.2482598607888631</v>
+        <v>0.1293814432989691</v>
       </c>
       <c r="X2">
-        <v>0.1058865178711606</v>
+        <v>0.1853530585031831</v>
       </c>
       <c r="AB2">
-        <v>0.1058865178711606</v>
+        <v>0.1853530585031831</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -654,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.07</v>
+        <v>-0.502</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -663,22 +666,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.330246913580247</v>
+        <v>-0.1486086441681468</v>
       </c>
       <c r="AK2">
-        <v>-0.6903225806451613</v>
+        <v>-0.2537917087967644</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.564327485380117</v>
+        <v>-0.5830429732868757</v>
+      </c>
+      <c r="AQ2">
+        <v>-31.6</v>
       </c>
     </row>
     <row r="3">
@@ -698,61 +704,64 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00874</v>
+        <v>0.0596</v>
       </c>
       <c r="E3">
-        <v>-0.00244</v>
+        <v>-0.00266</v>
       </c>
       <c r="G3">
-        <v>0.1387423935091278</v>
+        <v>0.1033722438391699</v>
       </c>
       <c r="H3">
-        <v>0.1387423935091278</v>
+        <v>0.1033722438391699</v>
       </c>
       <c r="I3">
-        <v>0.1269776876267749</v>
+        <v>0.1024643320363165</v>
       </c>
       <c r="J3">
-        <v>0.1071841069084835</v>
+        <v>0.08139806425756041</v>
       </c>
       <c r="K3">
-        <v>0.574</v>
+        <v>0.653</v>
       </c>
       <c r="L3">
-        <v>0.1164300202839757</v>
+        <v>0.08469520103761349</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.327</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.08427835051546392</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.5007656967840735</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.327</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.08427835051546392</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.5007656967840735</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1.07</v>
+        <v>0.502</v>
       </c>
       <c r="V3">
-        <v>0.2482598607888631</v>
+        <v>0.1293814432989691</v>
       </c>
       <c r="X3">
-        <v>0.1058865178711606</v>
+        <v>0.1853530585031831</v>
       </c>
       <c r="AB3">
-        <v>0.1058865178711606</v>
+        <v>0.1853530585031831</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -764,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.07</v>
+        <v>-0.502</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -773,22 +782,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.330246913580247</v>
+        <v>-0.1486086441681468</v>
       </c>
       <c r="AK3">
-        <v>-0.6903225806451613</v>
+        <v>-0.2537917087967644</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.564327485380117</v>
+        <v>-0.5830429732868757</v>
+      </c>
+      <c r="AQ3">
+        <v>-31.6</v>
       </c>
     </row>
   </sheetData>
